--- a/artfynd/S 1757-2025 artfynd.xlsx
+++ b/artfynd/S 1757-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY58"/>
+  <dimension ref="A1:AZ58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124879898</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124840778</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1003,6 +1018,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127150451</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1115,6 +1135,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124840777</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1227,6 +1252,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124879899</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1339,6 +1369,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124879903</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1446,6 +1481,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127150440</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1567,6 +1607,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124840776</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1679,6 +1724,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127150435</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1791,6 +1841,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124840782</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1903,6 +1958,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124879900</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2015,6 +2075,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124879901</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2127,6 +2192,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124879910</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2239,6 +2309,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124840769</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2351,6 +2426,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124840785</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2463,6 +2543,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124840786</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2575,6 +2660,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124879908</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2682,6 +2772,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127150831</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2794,6 +2889,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124840775</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2906,6 +3006,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124840807</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3018,6 +3123,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124840813</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3130,6 +3240,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124840820</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3227,6 +3342,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124840773</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3324,6 +3444,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124840783</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3436,6 +3561,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127150582</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3548,6 +3678,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124840790</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3660,6 +3795,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124840792</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3772,6 +3912,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124840794</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3884,6 +4029,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124840802</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3996,6 +4146,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124840806</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4108,6 +4263,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124840811</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4220,6 +4380,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124840814</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4317,6 +4482,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124840816</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4429,6 +4599,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124840818</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4541,6 +4716,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124879914</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4672,6 +4852,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127150222</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4774,6 +4959,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124840770</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4876,6 +5066,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124840771</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4978,6 +5173,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124840784</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5080,6 +5280,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124840800</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5197,6 +5402,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124840817</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5299,6 +5509,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124879909</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5396,6 +5611,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124879904</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5493,6 +5713,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124879907</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5605,6 +5830,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127150994</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5717,6 +5947,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127151439</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5829,6 +6064,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124840789</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5941,6 +6181,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124840793</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6053,6 +6298,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124840797</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6165,6 +6415,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124840804</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6277,6 +6532,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124840809</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6389,6 +6649,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124840812</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6501,6 +6766,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124840819</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6613,6 +6883,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124879911</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6725,6 +7000,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124879906</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6837,6 +7117,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124840788</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6949,8 +7234,72 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124840772</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>